--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260831.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>11,100,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.02%</t>
+          <t>16.22%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.62%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.08%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>1,115,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>4.10%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,087,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.96%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,785,000</t>
+          <t>810,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -792,29 +792,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.46%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>760,000</t>
+          <t>9,785,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.27%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -902,95 +902,95 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,550,000</t>
+          <t>650,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>650,000</t>
+          <t>2,640,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,640,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>3,400,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1012,73 +1012,73 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>11,000,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,050,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>11,000,000</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,737,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>12,000,000</t>
+          <t>1,737,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1188,73 +1188,73 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1474,129 +1474,129 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>220,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>220,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,35 +1701,39 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>8,765,278,891</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr"/>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12,457,357,495</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1737,17 +1741,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>RDI_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,654,126,552</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1755,20 +1759,38 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>2,162,354,124</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>RP_NTD</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>4,808,333,632</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr"/>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>3,300,089,384</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
